--- a/arquivos/id_tecnologia_facilidades.xlsx
+++ b/arquivos/id_tecnologia_facilidades.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F257064\Documents\Codes\NFV 3.0\arquivos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F257064\Documents\Codes\NFV 3.0\NFV 3.0\arquivos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C38E2FBF-1370-45DC-9348-D7F144F0702F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10EBBF1D-3BAF-43A0-8002-F742ED317243}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2088" yWindow="1872" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="62">
   <si>
     <t>FACILIDADE</t>
   </si>
@@ -206,9 +206,6 @@
     <t>RADIO IP</t>
   </si>
   <si>
-    <t>TERCEIROS BL</t>
-  </si>
-  <si>
     <t>FO GPON_RESID ETH PV</t>
   </si>
   <si>
@@ -219,6 +216,12 @@
   </si>
   <si>
     <t>CLARO BRASIL</t>
+  </si>
+  <si>
+    <t>TERCEIRO ETH</t>
+  </si>
+  <si>
+    <t>TERCEIRO BL</t>
   </si>
 </sst>
 </file>
@@ -584,7 +587,7 @@
         <v>4</v>
       </c>
       <c r="F2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G2">
         <v>8</v>
@@ -607,7 +610,7 @@
         <v>34</v>
       </c>
       <c r="F3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G3">
         <v>8</v>
@@ -630,7 +633,7 @@
         <v>35</v>
       </c>
       <c r="F4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G4">
         <v>8</v>
@@ -653,7 +656,7 @@
         <v>37</v>
       </c>
       <c r="F5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G5">
         <v>8</v>
@@ -676,7 +679,7 @@
         <v>38</v>
       </c>
       <c r="F6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G6">
         <v>8</v>
@@ -699,7 +702,7 @@
         <v>36</v>
       </c>
       <c r="F7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G7">
         <v>8</v>
@@ -719,10 +722,10 @@
         <v>52</v>
       </c>
       <c r="E8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G8">
         <v>8</v>
@@ -742,7 +745,7 @@
         <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G9">
         <v>8</v>
@@ -765,7 +768,7 @@
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G10">
         <v>8</v>
@@ -788,7 +791,7 @@
         <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G11">
         <v>8</v>
@@ -811,7 +814,7 @@
         <v>11</v>
       </c>
       <c r="F12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G12">
         <v>8</v>
@@ -834,7 +837,7 @@
         <v>12</v>
       </c>
       <c r="F13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G13">
         <v>8</v>
@@ -857,7 +860,7 @@
         <v>14</v>
       </c>
       <c r="F14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G14">
         <v>8</v>
@@ -880,7 +883,7 @@
         <v>16</v>
       </c>
       <c r="F15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G15">
         <v>8</v>
@@ -903,7 +906,7 @@
         <v>41</v>
       </c>
       <c r="F16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G16">
         <v>8</v>
@@ -926,7 +929,7 @@
         <v>54</v>
       </c>
       <c r="F17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G17">
         <v>8</v>
@@ -949,7 +952,7 @@
         <v>42</v>
       </c>
       <c r="F18" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G18">
         <v>8</v>
@@ -972,7 +975,7 @@
         <v>43</v>
       </c>
       <c r="F19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G19">
         <v>8</v>
@@ -989,10 +992,10 @@
         <v>40</v>
       </c>
       <c r="E20" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F20" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G20">
         <v>8</v>
@@ -1009,10 +1012,10 @@
         <v>40</v>
       </c>
       <c r="E21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F21" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G21">
         <v>8</v>
@@ -1035,7 +1038,7 @@
         <v>53</v>
       </c>
       <c r="F22" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G22">
         <v>8</v>
@@ -1058,7 +1061,7 @@
         <v>46</v>
       </c>
       <c r="F23" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G23">
         <v>8</v>
@@ -1075,7 +1078,7 @@
         <v>47</v>
       </c>
       <c r="E24" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
@@ -1089,7 +1092,7 @@
         <v>47</v>
       </c>
       <c r="E25" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -1106,7 +1109,7 @@
         <v>55</v>
       </c>
       <c r="F26" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G26">
         <v>8</v>
